--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Too Easy</v>
+        <v>True Colors</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-08</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Too Easy - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G2" t="str">
-        <v>1:54</v>
+        <v>3:39</v>
       </c>
       <c r="H2" t="str">
-        <v>Tinashe</v>
+        <v>Mike D</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L2" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Too Easy</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-08</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G3" t="str">
-        <v>2:58</v>
+        <v>1:54</v>
       </c>
       <c r="H3" t="str">
-        <v>Taylor Swift</v>
+        <v>Tinashe</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L3" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Love Sensation</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-08</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Love Sensation - Single</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H4" t="str">
-        <v>Madonna</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L4" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-08</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H5" t="str">
-        <v>Ozuna</v>
+        <v>Madonna</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L5" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Three Nations</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-08</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H6" t="str">
-        <v>21 Savage</v>
+        <v>Ozuna</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L6" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Champions (WC 26)</v>
+        <v>Three Nations</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-08</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G7" t="str">
-        <v>4:15</v>
+        <v>3:30</v>
       </c>
       <c r="H7" t="str">
-        <v>IShowSpeed</v>
+        <v>21 Savage</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L7" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENCERRONES</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-08</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>TEOFANIA</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>2:23</v>
+        <v>4:15</v>
       </c>
       <c r="H8" t="str">
-        <v>LENCHO</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L8" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Cowgirl</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-08</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G9" t="str">
-        <v>2:56</v>
+        <v>2:23</v>
       </c>
       <c r="H9" t="str">
-        <v>Shaboozey</v>
+        <v>LENCHO</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L9" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>PASSENGER</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-08</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>WILDCHILD</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G10" t="str">
-        <v>2:39</v>
+        <v>2:56</v>
       </c>
       <c r="H10" t="str">
-        <v>Alex Warren</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L10" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Secret Language</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-08</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Sweet Fortune</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G11" t="str">
-        <v>3:53</v>
+        <v>2:39</v>
       </c>
       <c r="H11" t="str">
-        <v>Ryan Beatty</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L11" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>High Hopes 3000</v>
+        <v>Secret Language</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-08</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G12" t="str">
-        <v>4:05</v>
+        <v>3:53</v>
       </c>
       <c r="H12" t="str">
-        <v>ROLE MODEL</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L12" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Vertical</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-08</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Emotional Junglist</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G13" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H13" t="str">
-        <v>Nia Archives</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L13" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>snake the drain</v>
+        <v>Vertical</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-08</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G14" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H14" t="str">
-        <v>Devon Again</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L14" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-08</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H15" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L15" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-08</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H16" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L16" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-08</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G17" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H17" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L17" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-08</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G18" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H18" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L18" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-08</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G19" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H19" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L19" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-08</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G20" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H20" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L20" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-08</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G21" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H21" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L21" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-08</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G22" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L22" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-08</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G23" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H23" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L23" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-08</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G24" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H24" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L24" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-08</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G25" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H25" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L25" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-08</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H26" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L26" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-08</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H27" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L27" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-08</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H28" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L28" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-08</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G29" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H29" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L29" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-08</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G30" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H30" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L30" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-08</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G31" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H31" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L31" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-08</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G32" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H32" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L32" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-08</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H33" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L33" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-08</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H34" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L34" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-08</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H35" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L35" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-08</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G36" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H36" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L36" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-08</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G37" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H37" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L37" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-08</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G38" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H38" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L38" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-08</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G39" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H39" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L39" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-08</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G40" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L40" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-08</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G41" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H41" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L41" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-08</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G42" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H42" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L42" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-08</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H43" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L43" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-08</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G44" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H44" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L44" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-08</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G45" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H45" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L45" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-08</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G46" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L46" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-08</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G47" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H47" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L47" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-08</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G48" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H48" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L48" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-08</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H49" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L49" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-08</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H50" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L50" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-08</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H51" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L51" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-08</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G52" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H52" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L52" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-08</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G53" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H53" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L53" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-08</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G54" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H54" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L54" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-08</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G55" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H55" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L55" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-08</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H56" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L56" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-08</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H57" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L57" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-08</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G58" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H58" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L58" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-08</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H59" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L59" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-08</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G60" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H60" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L60" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Miss Me More</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-08</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:43</v>
+        <v>2:06</v>
       </c>
       <c r="H61" t="str">
-        <v>Eric Nam</v>
+        <v>Pitbull</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L61" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-08</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G62" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H62" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L62" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-08</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H63" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L63" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-08</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H64" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L64" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-08</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G65" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H65" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L65" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-08</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L66" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-08</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H67" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L67" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-08</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H68" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L68" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-08</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G69" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L69" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-08</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H70" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L70" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-08</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H71" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L71" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-08</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H72" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L72" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-08</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H73" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L73" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-08</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H74" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L74" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-08</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H75" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L75" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-08</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H76" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L76" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-08</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H77" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L77" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-08</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H78" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L78" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-08</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G79" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H79" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L79" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-08</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H80" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L80" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-08</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G81" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H81" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L81" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-08</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G82" t="str">
         <v>3:19</v>
       </c>
       <c r="H82" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L82" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-08</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H83" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L83" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-08</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G84" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H84" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L84" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-08</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H85" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L85" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-08</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G86" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H86" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L86" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-08</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G87" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H87" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L87" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-08</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G88" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H88" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L88" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-08</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H89" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L89" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-08</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H90" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L90" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-08</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G91" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H91" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L91" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-08</v>
@@ -3871,68 +3871,106 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H92" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L92" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+      <c r="C93" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G93" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I93" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J93" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K93" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B93" t="str">
-        <v/>
-      </c>
-      <c r="C93" t="str">
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D93" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
+      <c r="D94" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G93" t="str">
+      <c r="G94" t="str">
         <v>3:51</v>
       </c>
-      <c r="H93" t="str">
+      <c r="H94" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I93" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J93" t="str">
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K93" t="str">
+      <c r="K94" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L93" t="str">
+      <c r="L94" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E94" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>True Colors</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Thank You</v>
+        <v>Alone Together</v>
       </c>
       <c r="G2" t="str">
-        <v>3:39</v>
+        <v>3:18</v>
       </c>
       <c r="H2" t="str">
-        <v>Mike D</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L2" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>High Hopes 3000</v>
+        <v>True Colors</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Thank You</v>
       </c>
       <c r="G13" t="str">
-        <v>4:05</v>
+        <v>3:39</v>
       </c>
       <c r="H13" t="str">
-        <v>ROLE MODEL</v>
+        <v>Mike D</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L13" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Vertical</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Emotional Junglist</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G14" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H14" t="str">
-        <v>Nia Archives</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L14" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>snake the drain</v>
+        <v>Vertical</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G15" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H15" t="str">
-        <v>Devon Again</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L15" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H16" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L16" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H17" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L17" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G18" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H18" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L18" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G19" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L19" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G20" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H20" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L20" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G21" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H21" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L21" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G22" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H22" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L22" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G23" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H23" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L23" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G24" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H24" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L24" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G25" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H25" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L25" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G26" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H26" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L26" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H27" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L27" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H28" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L28" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H29" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L29" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G30" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H30" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L30" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G31" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H31" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L31" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G32" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H32" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L32" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G33" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L33" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H34" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L34" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H35" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L35" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H36" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L36" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G37" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H37" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L37" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G38" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H38" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L38" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G39" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H39" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L39" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G40" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H40" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L40" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G41" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H41" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L41" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G42" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H42" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L42" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G43" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H43" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L43" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H44" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L44" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G45" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H45" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L45" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G46" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L46" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G47" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H47" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L47" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G48" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H48" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L48" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G49" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H49" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L49" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H50" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L50" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H51" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L51" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H52" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L52" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G53" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H53" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L53" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G54" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H54" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L54" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G55" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H55" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L55" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G56" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H56" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L56" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H57" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L57" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H58" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L58" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G59" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H59" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L59" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H60" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L60" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G61" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H61" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L61" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Miss Me More</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:43</v>
+        <v>2:06</v>
       </c>
       <c r="H62" t="str">
-        <v>Eric Nam</v>
+        <v>Pitbull</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L62" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G63" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H63" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L63" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H64" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L64" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H65" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L65" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G66" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H66" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L66" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H67" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L67" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H68" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L68" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H69" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L69" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G70" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H70" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L70" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H71" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L71" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H72" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L72" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H73" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L73" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H74" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L74" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H75" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L75" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H76" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L76" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H77" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L77" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H78" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L78" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H79" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L79" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G80" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H80" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L80" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H81" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L81" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G82" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H82" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L82" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G83" t="str">
         <v>3:19</v>
       </c>
       <c r="H83" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L83" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H84" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L84" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G85" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H85" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L85" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H86" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L86" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G87" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H87" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L87" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G88" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H88" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L88" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H89" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L89" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H90" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L90" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H91" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L91" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G92" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H92" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L92" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3909,68 +3909,106 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H93" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L93" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+      <c r="C94" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G94" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I94" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K94" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
-      </c>
-      <c r="C94" t="str">
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D94" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
+      <c r="D95" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G95" t="str">
         <v>3:51</v>
       </c>
-      <c r="H94" t="str">
+      <c r="H95" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I94" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J94" t="str">
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K94" t="str">
+      <c r="K95" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L94" t="str">
+      <c r="L95" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2754,1261 +2754,1299 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Miss Me More</v>
+        <v>Year of the Horse</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Year of the Horse - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:43</v>
+        <v>4:16</v>
       </c>
       <c r="H63" t="str">
-        <v>Eric Nam</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
       </c>
       <c r="L63" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Year of the Horse - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G64" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H64" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L64" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H65" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L65" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H66" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L66" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G67" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H67" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L67" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H68" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L68" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H69" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L69" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H70" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L70" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H71" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L71" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H72" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L72" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H73" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L73" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H74" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L74" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G75" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H75" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L75" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H76" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L76" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H77" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L77" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H78" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L78" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L79" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H80" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L80" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G81" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H81" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L81" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H82" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L82" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G83" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H83" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L83" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G84" t="str">
         <v>3:19</v>
       </c>
       <c r="H84" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L84" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H85" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L85" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G86" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H86" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L86" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H87" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L87" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G88" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H88" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L88" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G89" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H89" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L89" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G90" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H90" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L90" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H91" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L91" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H92" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L92" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G93" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H93" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L93" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H94" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L94" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+      <c r="C95" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G95" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I95" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K95" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B95" t="str">
-        <v/>
-      </c>
-      <c r="C95" t="str">
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D95" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
+      <c r="D96" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G96" t="str">
         <v>3:51</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H96" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I95" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J95" t="str">
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K96" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L95" t="str">
+      <c r="L96" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Eat For Peace</v>
+        <v>Better Man</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
+        <v>https://music.apple.com/us/song/better-man/6769823975</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-10</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Alone Together</v>
+        <v>Melodie</v>
       </c>
       <c r="G2" t="str">
-        <v>3:18</v>
+        <v>3:03</v>
       </c>
       <c r="H2" t="str">
-        <v>Show Me the Body</v>
+        <v>Slow Pulp</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/slow-pulp/1247711013</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
+        <v>https://music.apple.com/us/album/better-man/6769823972</v>
       </c>
       <c r="L2" t="str">
-        <v>Eat For Peace - Show Me the Body</v>
+        <v>Better Man - Slow Pulp</v>
       </c>
     </row>
     <row r="3">
@@ -632,7 +632,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/three-nations/6778672587</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-10</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Official FIFA World Cup 2026™ Album (Opening Ceremony Edition)</v>
       </c>
       <c r="G7" t="str">
         <v>3:30</v>
@@ -656,7 +656,7 @@
         <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/three-nations/6778672248</v>
       </c>
       <c r="L7" t="str">
         <v>Three Nations - 21 Savage</v>
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>True Colors</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-10</v>
@@ -869,25 +869,25 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Thank You</v>
+        <v>Alone Together</v>
       </c>
       <c r="G13" t="str">
-        <v>3:39</v>
+        <v>3:18</v>
       </c>
       <c r="H13" t="str">
-        <v>Mike D</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L13" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="14">
@@ -930,13 +930,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Vertical</v>
+        <v>True Colors</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-10</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Emotional Junglist</v>
+        <v>Thank You</v>
       </c>
       <c r="G15" t="str">
-        <v>2:36</v>
+        <v>3:39</v>
       </c>
       <c r="H15" t="str">
-        <v>Nia Archives</v>
+        <v>Mike D</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L15" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>snake the drain</v>
+        <v>Vertical</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-10</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G16" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H16" t="str">
-        <v>Devon Again</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L16" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-10</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H17" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L17" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-10</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H18" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L18" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-10</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G19" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L19" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-10</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G20" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H20" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L20" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-10</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G21" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H21" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L21" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-10</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G22" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H22" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L22" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-10</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G23" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H23" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L23" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-10</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G24" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H24" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L24" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-10</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G25" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H25" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L25" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-10</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G26" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H26" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L26" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-10</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G27" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H27" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L27" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-10</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H28" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L28" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-10</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H29" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L29" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-10</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H30" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L30" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-10</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G31" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H31" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L31" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-10</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G32" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H32" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L32" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-10</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H33" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L33" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-10</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G34" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L34" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-10</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H35" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L35" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-10</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H36" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L36" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-10</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H37" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L37" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-10</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G38" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L38" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-10</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G39" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H39" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L39" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-10</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G40" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H40" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L40" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-10</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G41" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H41" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L41" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-10</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G42" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H42" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L42" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-10</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G43" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H43" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L43" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-10</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G44" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H44" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L44" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-10</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H45" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L45" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-10</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G46" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H46" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L46" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-10</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G47" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L47" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-10</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G48" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H48" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L48" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-10</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G49" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H49" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L49" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-10</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G50" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H50" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L50" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-10</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H51" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L51" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-10</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H52" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L52" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-10</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H53" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L53" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-10</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G54" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H54" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L54" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-10</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G55" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H55" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L55" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-10</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G56" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H56" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L56" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-10</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G57" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H57" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L57" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-10</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H58" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L58" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-10</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L59" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-10</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G60" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H60" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L60" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-10</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H61" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L61" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-10</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G62" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H62" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L62" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Year of the Horse</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-10</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Year of the Horse - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:16</v>
+        <v>2:06</v>
       </c>
       <c r="H63" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Pitbull</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L63" t="str">
-        <v>Year of the Horse - Aly &amp; AJ</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Miss Me More</v>
+        <v>Year of the Horse</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-10</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Year of the Horse - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:43</v>
+        <v>4:16</v>
       </c>
       <c r="H64" t="str">
-        <v>Eric Nam</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
       </c>
       <c r="L64" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Year of the Horse - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-10</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G65" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H65" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L65" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-10</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H66" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L66" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-10</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H67" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L67" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-10</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G68" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L68" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-10</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H69" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L69" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-10</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H70" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L70" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-10</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H71" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L71" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-10</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H72" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L72" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-10</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H73" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L73" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-10</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H74" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L74" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-10</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G75" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H75" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L75" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-10</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G76" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H76" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L76" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-10</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H77" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L77" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-10</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H78" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L78" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-10</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H79" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L79" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-10</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H80" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L80" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-10</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H81" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L81" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-10</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G82" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H82" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L82" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-10</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H83" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L83" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-10</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G84" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L84" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-10</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G85" t="str">
         <v>3:19</v>
       </c>
       <c r="H85" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L85" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-10</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H86" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L86" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-10</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G87" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H87" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L87" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-10</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H88" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L88" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-10</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G89" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H89" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L89" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-10</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G90" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H90" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L90" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-10</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G91" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H91" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L91" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-10</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H92" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L92" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-10</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H93" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L93" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-10</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G94" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H94" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L94" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-10</v>
@@ -3985,68 +3985,106 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H95" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L95" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+      <c r="C96" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I96" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K96" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
-      </c>
-      <c r="C96" t="str">
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D96" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
+      <c r="D97" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G96" t="str">
+      <c r="G97" t="str">
         <v>3:51</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H97" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I96" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J96" t="str">
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K97" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L96" t="str">
+      <c r="L97" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/better-man/6769823975</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/three-nations/6778672587</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="E97" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Better Man</v>
+        <v>Burning Out</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/better-man/6769823975</v>
+        <v>https://music.apple.com/us/song/burning-out/6772337604</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-11</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Melodie</v>
+        <v>Burning Out - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:03</v>
+        <v>3:18</v>
       </c>
       <c r="H2" t="str">
-        <v>Slow Pulp</v>
+        <v>The Linda Lindas</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/slow-pulp/1247711013</v>
+        <v>https://music.apple.com/us/artist/the-linda-lindas/1525944355</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/better-man/6769823972</v>
+        <v>https://music.apple.com/us/album/burning-out/6772337602</v>
       </c>
       <c r="L2" t="str">
-        <v>Better Man - Slow Pulp</v>
+        <v>Burning Out - The Linda Lindas</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Eat For Peace</v>
+        <v>Better Man</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
+        <v>https://music.apple.com/us/song/better-man/6769823975</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-11</v>
@@ -869,25 +869,25 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Alone Together</v>
+        <v>Melodie</v>
       </c>
       <c r="G13" t="str">
-        <v>3:18</v>
+        <v>3:03</v>
       </c>
       <c r="H13" t="str">
-        <v>Show Me the Body</v>
+        <v>Slow Pulp</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/slow-pulp/1247711013</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
+        <v>https://music.apple.com/us/album/better-man/6769823972</v>
       </c>
       <c r="L13" t="str">
-        <v>Eat For Peace - Show Me the Body</v>
+        <v>Better Man - Slow Pulp</v>
       </c>
     </row>
     <row r="14">
@@ -930,13 +930,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>True Colors</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-11</v>
@@ -945,25 +945,25 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Thank You</v>
+        <v>Alone Together</v>
       </c>
       <c r="G15" t="str">
-        <v>3:39</v>
+        <v>3:18</v>
       </c>
       <c r="H15" t="str">
-        <v>Mike D</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L15" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="16">
@@ -1006,13 +1006,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>snake the drain</v>
+        <v>True Colors</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-11</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G17" t="str">
-        <v>3:08</v>
+        <v>3:39</v>
       </c>
       <c r="H17" t="str">
-        <v>Devon Again</v>
+        <v>Mike D</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L17" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-11</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L18" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-11</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H19" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L19" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-11</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G20" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H20" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L20" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-11</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G21" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H21" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L21" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-11</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G22" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H22" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L22" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-11</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G23" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H23" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L23" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-11</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G24" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H24" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L24" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-11</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G25" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H25" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L25" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-11</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G26" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H26" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L26" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-11</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G27" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H27" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L27" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-11</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G28" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H28" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L28" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-11</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H29" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L29" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-11</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H30" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L30" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-11</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H31" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L31" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-11</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G32" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H32" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L32" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-11</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G33" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H33" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L33" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-11</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H34" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L34" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-11</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G35" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L35" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-11</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H36" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L36" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-11</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H37" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L37" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-11</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H38" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L38" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-11</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G39" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L39" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-11</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G40" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H40" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L40" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-11</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G41" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H41" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L41" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-11</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G42" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H42" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L42" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-11</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G43" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H43" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L43" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-11</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G44" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H44" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L44" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-11</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G45" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H45" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L45" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-11</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H46" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L46" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-11</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G47" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H47" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L47" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-11</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G48" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H48" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L48" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-11</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G49" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H49" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L49" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-11</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G50" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H50" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L50" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-11</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G51" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H51" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L51" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-11</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H52" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L52" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-11</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H53" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L53" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-11</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L54" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-11</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G55" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H55" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L55" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-11</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G56" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L56" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-11</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G57" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H57" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L57" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-11</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G58" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L58" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-11</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H59" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L59" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-11</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H60" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L60" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-11</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G61" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L61" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-11</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G62" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H62" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L62" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-11</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G63" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H63" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L63" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Year of the Horse</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-11</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Year of the Horse - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:16</v>
+        <v>2:06</v>
       </c>
       <c r="H64" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Pitbull</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L64" t="str">
-        <v>Year of the Horse - Aly &amp; AJ</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Miss Me More</v>
+        <v>Year of the Horse</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-11</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Year of the Horse - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:43</v>
+        <v>4:16</v>
       </c>
       <c r="H65" t="str">
-        <v>Eric Nam</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
       </c>
       <c r="L65" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Year of the Horse - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-11</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G66" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H66" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L66" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-11</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H67" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L67" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-11</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H68" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L68" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-11</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G69" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H69" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L69" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-11</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H70" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L70" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-11</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H71" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L71" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-11</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H72" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L72" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-11</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H73" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L73" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-11</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H74" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L74" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-11</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H75" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L75" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-11</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G76" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H76" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L76" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-11</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G77" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H77" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L77" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-11</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H78" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L78" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-11</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H79" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L79" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-11</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H80" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L80" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-11</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H81" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L81" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-11</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H82" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L82" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-11</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G83" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H83" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L83" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-11</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H84" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L84" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-11</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G85" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H85" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L85" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-11</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G86" t="str">
         <v>3:19</v>
       </c>
       <c r="H86" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L86" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-11</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H87" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L87" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-11</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G88" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H88" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L88" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-11</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H89" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L89" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-11</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G90" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H90" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L90" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-11</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G91" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H91" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L91" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-11</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G92" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H92" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L92" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-11</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H93" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L93" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-11</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H94" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L94" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-11</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G95" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L95" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-11</v>
@@ -4023,68 +4023,106 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H96" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L96" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+      <c r="C97" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G97" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I97" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K97" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B97" t="str">
-        <v/>
-      </c>
-      <c r="C97" t="str">
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D97" t="str">
-        <v>2026-06-11</v>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
+      <c r="D98" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G97" t="str">
+      <c r="G98" t="str">
         <v>3:51</v>
       </c>
-      <c r="H97" t="str">
+      <c r="H98" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I97" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J97" t="str">
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K98" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L97" t="str">
+      <c r="L98" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
   </ignoredErrors>
 </worksheet>
 </file>